--- a/DATA/People_list.xlsx
+++ b/DATA/People_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Coren\Documents\Python Projects\Face_Quizz\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6923EE30-131B-4D1B-AB9F-3E116B302B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBF2D8-6734-45EF-9EB2-5DE851A40F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="1152">
   <si>
     <t>Name</t>
   </si>
@@ -2644,9 +2644,6 @@
   </si>
   <si>
     <t>Artist known with his wife Jeanne-Claude for their large-scale, site-specific environmental installations and wrapped buildings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male </t>
   </si>
   <si>
     <t>Cindy Sherman</t>
@@ -11287,7 +11284,7 @@
         <v>871</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>872</v>
+        <v>7</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>79</v>
@@ -11295,13 +11292,13 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="B430" s="1">
+        <v>3</v>
+      </c>
+      <c r="C430" s="1" t="s">
         <v>873</v>
-      </c>
-      <c r="B430" s="1">
-        <v>3</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>874</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>11</v>
@@ -11312,13 +11309,13 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="B431" s="1">
+        <v>3</v>
+      </c>
+      <c r="C431" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="B431" s="1">
-        <v>3</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>7</v>
@@ -11329,13 +11326,13 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="B432" s="1">
+        <v>3</v>
+      </c>
+      <c r="C432" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="B432" s="1">
-        <v>3</v>
-      </c>
-      <c r="C432" s="1" t="s">
-        <v>878</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>7</v>
@@ -11346,13 +11343,13 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="B433" s="1">
+        <v>3</v>
+      </c>
+      <c r="C433" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="B433" s="1">
-        <v>3</v>
-      </c>
-      <c r="C433" s="1" t="s">
-        <v>880</v>
       </c>
       <c r="D433" s="1" t="s">
         <v>7</v>
@@ -11363,13 +11360,13 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="B434" s="1">
+        <v>3</v>
+      </c>
+      <c r="C434" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="B434" s="1">
-        <v>3</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>882</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>7</v>
@@ -11380,13 +11377,13 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="B435" s="1">
+        <v>3</v>
+      </c>
+      <c r="C435" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="B435" s="1">
-        <v>3</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>7</v>
@@ -11397,13 +11394,13 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="B436" s="1">
+        <v>3</v>
+      </c>
+      <c r="C436" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="B436" s="1">
-        <v>3</v>
-      </c>
-      <c r="C436" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>7</v>
@@ -11414,13 +11411,13 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="B437" s="1">
+        <v>3</v>
+      </c>
+      <c r="C437" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="B437" s="1">
-        <v>3</v>
-      </c>
-      <c r="C437" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>7</v>
@@ -11431,13 +11428,13 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="B438" s="1">
+        <v>3</v>
+      </c>
+      <c r="C438" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="B438" s="1">
-        <v>3</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>7</v>
@@ -11448,13 +11445,13 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="B439" s="1">
+        <v>3</v>
+      </c>
+      <c r="C439" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="B439" s="1">
-        <v>3</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>892</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>7</v>
@@ -11465,13 +11462,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="B440" s="1">
+        <v>3</v>
+      </c>
+      <c r="C440" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="B440" s="1">
-        <v>3</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>894</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>11</v>
@@ -11482,13 +11479,13 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="B441" s="1">
+        <v>3</v>
+      </c>
+      <c r="C441" s="1" t="s">
         <v>895</v>
-      </c>
-      <c r="B441" s="1">
-        <v>3</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>896</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>11</v>
@@ -11499,13 +11496,13 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="B442" s="1">
+        <v>3</v>
+      </c>
+      <c r="C442" s="1" t="s">
         <v>897</v>
-      </c>
-      <c r="B442" s="1">
-        <v>3</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>898</v>
       </c>
       <c r="D442" s="1" t="s">
         <v>7</v>
@@ -11516,13 +11513,13 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="B443" s="1">
+        <v>3</v>
+      </c>
+      <c r="C443" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="B443" s="1">
-        <v>3</v>
-      </c>
-      <c r="C443" s="1" t="s">
-        <v>900</v>
       </c>
       <c r="D443" s="1" t="s">
         <v>7</v>
@@ -11533,13 +11530,13 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="B444" s="1">
+        <v>3</v>
+      </c>
+      <c r="C444" s="1" t="s">
         <v>901</v>
-      </c>
-      <c r="B444" s="1">
-        <v>3</v>
-      </c>
-      <c r="C444" s="1" t="s">
-        <v>902</v>
       </c>
       <c r="D444" s="1" t="s">
         <v>7</v>
@@ -11550,13 +11547,13 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="B445" s="1">
+        <v>3</v>
+      </c>
+      <c r="C445" s="1" t="s">
         <v>903</v>
-      </c>
-      <c r="B445" s="1">
-        <v>3</v>
-      </c>
-      <c r="C445" s="1" t="s">
-        <v>904</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>7</v>
@@ -11567,13 +11564,13 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B446" s="1">
+        <v>3</v>
+      </c>
+      <c r="C446" s="1" t="s">
         <v>905</v>
-      </c>
-      <c r="B446" s="1">
-        <v>3</v>
-      </c>
-      <c r="C446" s="1" t="s">
-        <v>906</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>7</v>
@@ -11584,13 +11581,13 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="B447" s="1">
+        <v>3</v>
+      </c>
+      <c r="C447" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="B447" s="1">
-        <v>3</v>
-      </c>
-      <c r="C447" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>7</v>
@@ -11601,13 +11598,13 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="B448" s="1">
+        <v>3</v>
+      </c>
+      <c r="C448" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="B448" s="1">
-        <v>3</v>
-      </c>
-      <c r="C448" s="1" t="s">
-        <v>910</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>11</v>
@@ -11618,13 +11615,13 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="B449" s="1">
+        <v>3</v>
+      </c>
+      <c r="C449" s="1" t="s">
         <v>911</v>
-      </c>
-      <c r="B449" s="1">
-        <v>3</v>
-      </c>
-      <c r="C449" s="1" t="s">
-        <v>912</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>11</v>
@@ -11635,13 +11632,13 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="B450" s="1">
+        <v>3</v>
+      </c>
+      <c r="C450" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="B450" s="1">
-        <v>3</v>
-      </c>
-      <c r="C450" s="1" t="s">
-        <v>914</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>7</v>
@@ -11652,13 +11649,13 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="B451" s="1">
+        <v>3</v>
+      </c>
+      <c r="C451" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="B451" s="1">
-        <v>3</v>
-      </c>
-      <c r="C451" s="1" t="s">
-        <v>916</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>7</v>
@@ -11669,13 +11666,13 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="B452" s="1">
+        <v>3</v>
+      </c>
+      <c r="C452" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="B452" s="1">
-        <v>3</v>
-      </c>
-      <c r="C452" s="1" t="s">
-        <v>918</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>7</v>
@@ -11686,13 +11683,13 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="B453" s="1">
+        <v>3</v>
+      </c>
+      <c r="C453" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="B453" s="1">
-        <v>3</v>
-      </c>
-      <c r="C453" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>7</v>
@@ -11703,13 +11700,13 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="B454" s="1">
+        <v>3</v>
+      </c>
+      <c r="C454" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="B454" s="1">
-        <v>3</v>
-      </c>
-      <c r="C454" s="1" t="s">
-        <v>922</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>7</v>
@@ -11720,13 +11717,13 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="B455" s="1">
+        <v>3</v>
+      </c>
+      <c r="C455" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="B455" s="1">
-        <v>3</v>
-      </c>
-      <c r="C455" s="1" t="s">
-        <v>924</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>7</v>
@@ -11737,13 +11734,13 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="B456" s="1">
+        <v>3</v>
+      </c>
+      <c r="C456" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="B456" s="1">
-        <v>3</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>926</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>7</v>
@@ -11754,13 +11751,13 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="B457" s="1">
+        <v>3</v>
+      </c>
+      <c r="C457" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="B457" s="1">
-        <v>3</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>928</v>
       </c>
       <c r="D457" s="1" t="s">
         <v>11</v>
@@ -11771,13 +11768,13 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B458" s="1">
+        <v>3</v>
+      </c>
+      <c r="C458" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="B458" s="1">
-        <v>3</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>930</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>7</v>
@@ -11788,13 +11785,13 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="B459" s="1">
+        <v>3</v>
+      </c>
+      <c r="C459" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="B459" s="1">
-        <v>3</v>
-      </c>
-      <c r="C459" s="1" t="s">
-        <v>932</v>
       </c>
       <c r="D459" s="1" t="s">
         <v>7</v>
@@ -11805,13 +11802,13 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="B460" s="1">
+        <v>3</v>
+      </c>
+      <c r="C460" s="1" t="s">
         <v>933</v>
-      </c>
-      <c r="B460" s="1">
-        <v>3</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>934</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>7</v>
@@ -11822,13 +11819,13 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="B461" s="1">
+        <v>3</v>
+      </c>
+      <c r="C461" s="1" t="s">
         <v>935</v>
-      </c>
-      <c r="B461" s="1">
-        <v>3</v>
-      </c>
-      <c r="C461" s="1" t="s">
-        <v>936</v>
       </c>
       <c r="D461" s="1" t="s">
         <v>7</v>
@@ -11839,13 +11836,13 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="B462" s="1">
+        <v>3</v>
+      </c>
+      <c r="C462" s="1" t="s">
         <v>937</v>
-      </c>
-      <c r="B462" s="1">
-        <v>3</v>
-      </c>
-      <c r="C462" s="1" t="s">
-        <v>938</v>
       </c>
       <c r="D462" s="1" t="s">
         <v>7</v>
@@ -11856,13 +11853,13 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="B463" s="1">
+        <v>3</v>
+      </c>
+      <c r="C463" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="B463" s="1">
-        <v>3</v>
-      </c>
-      <c r="C463" s="1" t="s">
-        <v>940</v>
       </c>
       <c r="D463" s="1" t="s">
         <v>11</v>
@@ -11873,13 +11870,13 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="B464" s="1">
+        <v>3</v>
+      </c>
+      <c r="C464" s="1" t="s">
         <v>941</v>
-      </c>
-      <c r="B464" s="1">
-        <v>3</v>
-      </c>
-      <c r="C464" s="1" t="s">
-        <v>942</v>
       </c>
       <c r="D464" s="1" t="s">
         <v>11</v>
@@ -11890,13 +11887,13 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="B465" s="1">
+        <v>3</v>
+      </c>
+      <c r="C465" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="B465" s="1">
-        <v>3</v>
-      </c>
-      <c r="C465" s="1" t="s">
-        <v>944</v>
       </c>
       <c r="D465" s="1" t="s">
         <v>7</v>
@@ -11907,13 +11904,13 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="B466" s="1">
+        <v>3</v>
+      </c>
+      <c r="C466" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="B466" s="1">
-        <v>3</v>
-      </c>
-      <c r="C466" s="1" t="s">
-        <v>946</v>
       </c>
       <c r="D466" s="1" t="s">
         <v>11</v>
@@ -11924,13 +11921,13 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="B467" s="1">
+        <v>3</v>
+      </c>
+      <c r="C467" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="B467" s="1">
-        <v>3</v>
-      </c>
-      <c r="C467" s="1" t="s">
-        <v>948</v>
       </c>
       <c r="D467" s="1" t="s">
         <v>11</v>
@@ -11941,13 +11938,13 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="B468" s="1">
+        <v>3</v>
+      </c>
+      <c r="C468" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="B468" s="1">
-        <v>3</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>950</v>
       </c>
       <c r="D468" s="1" t="s">
         <v>7</v>
@@ -11958,13 +11955,13 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="B469" s="1">
+        <v>3</v>
+      </c>
+      <c r="C469" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="B469" s="1">
-        <v>3</v>
-      </c>
-      <c r="C469" s="1" t="s">
-        <v>952</v>
       </c>
       <c r="D469" s="1" t="s">
         <v>11</v>
@@ -11975,13 +11972,13 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="B470" s="1">
+        <v>3</v>
+      </c>
+      <c r="C470" s="1" t="s">
         <v>953</v>
-      </c>
-      <c r="B470" s="1">
-        <v>3</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>954</v>
       </c>
       <c r="D470" s="1" t="s">
         <v>7</v>
@@ -11992,13 +11989,13 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="B471" s="1">
+        <v>3</v>
+      </c>
+      <c r="C471" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="B471" s="1">
-        <v>3</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>956</v>
       </c>
       <c r="D471" s="1" t="s">
         <v>7</v>
@@ -12009,13 +12006,13 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="B472" s="1">
+        <v>3</v>
+      </c>
+      <c r="C472" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="B472" s="1">
-        <v>3</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>958</v>
       </c>
       <c r="D472" s="1" t="s">
         <v>7</v>
@@ -12026,13 +12023,13 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="B473" s="1">
+        <v>3</v>
+      </c>
+      <c r="C473" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="B473" s="1">
-        <v>3</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>960</v>
       </c>
       <c r="D473" s="1" t="s">
         <v>7</v>
@@ -12043,13 +12040,13 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="B474" s="1">
+        <v>3</v>
+      </c>
+      <c r="C474" s="1" t="s">
         <v>961</v>
-      </c>
-      <c r="B474" s="1">
-        <v>3</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>962</v>
       </c>
       <c r="D474" s="1" t="s">
         <v>7</v>
@@ -12060,13 +12057,13 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="B475" s="1">
+        <v>3</v>
+      </c>
+      <c r="C475" s="1" t="s">
         <v>963</v>
-      </c>
-      <c r="B475" s="1">
-        <v>3</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>964</v>
       </c>
       <c r="D475" s="1" t="s">
         <v>7</v>
@@ -12077,13 +12074,13 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="B476" s="1">
+        <v>3</v>
+      </c>
+      <c r="C476" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="B476" s="1">
-        <v>3</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>966</v>
       </c>
       <c r="D476" s="1" t="s">
         <v>7</v>
@@ -12094,13 +12091,13 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="B477" s="1">
+        <v>3</v>
+      </c>
+      <c r="C477" s="1" t="s">
         <v>967</v>
-      </c>
-      <c r="B477" s="1">
-        <v>3</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>968</v>
       </c>
       <c r="D477" s="1" t="s">
         <v>11</v>
@@ -12111,13 +12108,13 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="B478" s="1">
+        <v>3</v>
+      </c>
+      <c r="C478" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="B478" s="1">
-        <v>3</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>970</v>
       </c>
       <c r="D478" s="1" t="s">
         <v>7</v>
@@ -12128,13 +12125,13 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="B479" s="1">
+        <v>3</v>
+      </c>
+      <c r="C479" s="1" t="s">
         <v>971</v>
-      </c>
-      <c r="B479" s="1">
-        <v>3</v>
-      </c>
-      <c r="C479" s="1" t="s">
-        <v>972</v>
       </c>
       <c r="D479" s="1" t="s">
         <v>7</v>
@@ -12145,13 +12142,13 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="B480" s="1">
+        <v>3</v>
+      </c>
+      <c r="C480" s="1" t="s">
         <v>973</v>
-      </c>
-      <c r="B480" s="1">
-        <v>3</v>
-      </c>
-      <c r="C480" s="1" t="s">
-        <v>974</v>
       </c>
       <c r="D480" s="1" t="s">
         <v>11</v>
@@ -12162,13 +12159,13 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="B481" s="1">
+        <v>3</v>
+      </c>
+      <c r="C481" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="B481" s="1">
-        <v>3</v>
-      </c>
-      <c r="C481" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="D481" s="1" t="s">
         <v>7</v>
@@ -12179,13 +12176,13 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="B482" s="1">
+        <v>3</v>
+      </c>
+      <c r="C482" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="B482" s="1">
-        <v>3</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>978</v>
       </c>
       <c r="D482" s="1" t="s">
         <v>7</v>
@@ -12196,13 +12193,13 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="B483" s="1">
+        <v>3</v>
+      </c>
+      <c r="C483" s="1" t="s">
         <v>979</v>
-      </c>
-      <c r="B483" s="1">
-        <v>3</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>980</v>
       </c>
       <c r="D483" s="1" t="s">
         <v>11</v>
@@ -12213,13 +12210,13 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="B484" s="1">
+        <v>3</v>
+      </c>
+      <c r="C484" s="1" t="s">
         <v>981</v>
-      </c>
-      <c r="B484" s="1">
-        <v>3</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>982</v>
       </c>
       <c r="D484" s="1" t="s">
         <v>7</v>
@@ -12230,13 +12227,13 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B485" s="1">
+        <v>3</v>
+      </c>
+      <c r="C485" s="1" t="s">
         <v>983</v>
-      </c>
-      <c r="B485" s="1">
-        <v>3</v>
-      </c>
-      <c r="C485" s="1" t="s">
-        <v>984</v>
       </c>
       <c r="D485" s="1" t="s">
         <v>11</v>
@@ -12247,13 +12244,13 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="B486" s="1">
+        <v>3</v>
+      </c>
+      <c r="C486" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="B486" s="1">
-        <v>3</v>
-      </c>
-      <c r="C486" s="1" t="s">
-        <v>986</v>
       </c>
       <c r="D486" s="1" t="s">
         <v>11</v>
@@ -12264,13 +12261,13 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="B487" s="1">
+        <v>3</v>
+      </c>
+      <c r="C487" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="B487" s="1">
-        <v>3</v>
-      </c>
-      <c r="C487" s="1" t="s">
-        <v>988</v>
       </c>
       <c r="D487" s="1" t="s">
         <v>7</v>
@@ -12281,13 +12278,13 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="B488" s="1">
+        <v>3</v>
+      </c>
+      <c r="C488" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="B488" s="1">
-        <v>3</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>990</v>
       </c>
       <c r="D488" s="1" t="s">
         <v>7</v>
@@ -12298,13 +12295,13 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="B489" s="1">
+        <v>3</v>
+      </c>
+      <c r="C489" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="B489" s="1">
-        <v>3</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>992</v>
       </c>
       <c r="D489" s="1" t="s">
         <v>7</v>
@@ -12315,13 +12312,13 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="B490" s="1">
+        <v>3</v>
+      </c>
+      <c r="C490" s="1" t="s">
         <v>993</v>
-      </c>
-      <c r="B490" s="1">
-        <v>3</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>994</v>
       </c>
       <c r="D490" s="1" t="s">
         <v>7</v>
@@ -12332,13 +12329,13 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="B491" s="1">
+        <v>3</v>
+      </c>
+      <c r="C491" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="B491" s="1">
-        <v>3</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="D491" s="1" t="s">
         <v>11</v>
@@ -12349,13 +12346,13 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B492" s="1">
+        <v>3</v>
+      </c>
+      <c r="C492" s="1" t="s">
         <v>997</v>
-      </c>
-      <c r="B492" s="1">
-        <v>3</v>
-      </c>
-      <c r="C492" s="1" t="s">
-        <v>998</v>
       </c>
       <c r="D492" s="1" t="s">
         <v>7</v>
@@ -12366,13 +12363,13 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="B493" s="1">
+        <v>3</v>
+      </c>
+      <c r="C493" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="B493" s="1">
-        <v>3</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>1000</v>
       </c>
       <c r="D493" s="1" t="s">
         <v>11</v>
@@ -12383,13 +12380,13 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B494" s="1">
+        <v>3</v>
+      </c>
+      <c r="C494" s="1" t="s">
         <v>1001</v>
-      </c>
-      <c r="B494" s="1">
-        <v>3</v>
-      </c>
-      <c r="C494" s="1" t="s">
-        <v>1002</v>
       </c>
       <c r="D494" s="1" t="s">
         <v>7</v>
@@ -12400,13 +12397,13 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B495" s="1">
+        <v>3</v>
+      </c>
+      <c r="C495" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="B495" s="1">
-        <v>3</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>1004</v>
       </c>
       <c r="D495" s="1" t="s">
         <v>7</v>
@@ -12417,13 +12414,13 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B496" s="1">
+        <v>3</v>
+      </c>
+      <c r="C496" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="B496" s="1">
-        <v>3</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>1006</v>
       </c>
       <c r="D496" s="1" t="s">
         <v>7</v>
@@ -12434,13 +12431,13 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B497" s="1">
+        <v>3</v>
+      </c>
+      <c r="C497" s="1" t="s">
         <v>1007</v>
-      </c>
-      <c r="B497" s="1">
-        <v>3</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>1008</v>
       </c>
       <c r="D497" s="1" t="s">
         <v>7</v>
@@ -12451,13 +12448,13 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B498" s="1">
+        <v>3</v>
+      </c>
+      <c r="C498" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="B498" s="1">
-        <v>3</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>1010</v>
       </c>
       <c r="D498" s="1" t="s">
         <v>11</v>
@@ -12468,13 +12465,13 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B499" s="1">
+        <v>3</v>
+      </c>
+      <c r="C499" s="1" t="s">
         <v>1011</v>
-      </c>
-      <c r="B499" s="1">
-        <v>3</v>
-      </c>
-      <c r="C499" s="1" t="s">
-        <v>1012</v>
       </c>
       <c r="D499" s="1" t="s">
         <v>7</v>
@@ -12485,13 +12482,13 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B500" s="1">
+        <v>3</v>
+      </c>
+      <c r="C500" s="1" t="s">
         <v>1013</v>
-      </c>
-      <c r="B500" s="1">
-        <v>3</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>1014</v>
       </c>
       <c r="D500" s="1" t="s">
         <v>7</v>
@@ -12502,13 +12499,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B501" s="1">
+        <v>3</v>
+      </c>
+      <c r="C501" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="B501" s="1">
-        <v>3</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>1016</v>
       </c>
       <c r="D501" s="1" t="s">
         <v>7</v>
@@ -12519,13 +12516,13 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B502" s="1">
+        <v>3</v>
+      </c>
+      <c r="C502" s="1" t="s">
         <v>1017</v>
-      </c>
-      <c r="B502" s="1">
-        <v>3</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>1018</v>
       </c>
       <c r="D502" s="1" t="s">
         <v>11</v>
@@ -12536,13 +12533,13 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B503" s="1">
+        <v>3</v>
+      </c>
+      <c r="C503" s="1" t="s">
         <v>1019</v>
-      </c>
-      <c r="B503" s="1">
-        <v>3</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>1020</v>
       </c>
       <c r="D503" s="1" t="s">
         <v>7</v>
@@ -12553,13 +12550,13 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B504" s="1">
+        <v>3</v>
+      </c>
+      <c r="C504" s="1" t="s">
         <v>1021</v>
-      </c>
-      <c r="B504" s="1">
-        <v>3</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>1022</v>
       </c>
       <c r="D504" s="1" t="s">
         <v>11</v>
@@ -12570,13 +12567,13 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B505" s="1">
+        <v>3</v>
+      </c>
+      <c r="C505" s="1" t="s">
         <v>1023</v>
-      </c>
-      <c r="B505" s="1">
-        <v>3</v>
-      </c>
-      <c r="C505" s="1" t="s">
-        <v>1024</v>
       </c>
       <c r="D505" s="1" t="s">
         <v>11</v>
@@ -12587,13 +12584,13 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B506" s="1">
+        <v>3</v>
+      </c>
+      <c r="C506" s="1" t="s">
         <v>1025</v>
-      </c>
-      <c r="B506" s="1">
-        <v>3</v>
-      </c>
-      <c r="C506" s="1" t="s">
-        <v>1026</v>
       </c>
       <c r="D506" s="1" t="s">
         <v>7</v>
@@ -12604,13 +12601,13 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B507" s="1">
+        <v>3</v>
+      </c>
+      <c r="C507" s="1" t="s">
         <v>1027</v>
-      </c>
-      <c r="B507" s="1">
-        <v>3</v>
-      </c>
-      <c r="C507" s="1" t="s">
-        <v>1028</v>
       </c>
       <c r="D507" s="1" t="s">
         <v>7</v>
@@ -12621,13 +12618,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B508" s="1">
+        <v>3</v>
+      </c>
+      <c r="C508" s="1" t="s">
         <v>1029</v>
-      </c>
-      <c r="B508" s="1">
-        <v>3</v>
-      </c>
-      <c r="C508" s="1" t="s">
-        <v>1030</v>
       </c>
       <c r="D508" s="1" t="s">
         <v>11</v>
@@ -12638,13 +12635,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B509" s="1">
+        <v>3</v>
+      </c>
+      <c r="C509" s="1" t="s">
         <v>1031</v>
-      </c>
-      <c r="B509" s="1">
-        <v>3</v>
-      </c>
-      <c r="C509" s="1" t="s">
-        <v>1032</v>
       </c>
       <c r="D509" s="1" t="s">
         <v>11</v>
@@ -12655,13 +12652,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B510" s="1">
+        <v>3</v>
+      </c>
+      <c r="C510" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="B510" s="1">
-        <v>3</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>1034</v>
       </c>
       <c r="D510" s="1" t="s">
         <v>11</v>
@@ -12672,13 +12669,13 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B511" s="1">
+        <v>3</v>
+      </c>
+      <c r="C511" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="B511" s="1">
-        <v>3</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>1036</v>
       </c>
       <c r="D511" s="1" t="s">
         <v>11</v>
@@ -12689,13 +12686,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B512" s="1">
+        <v>3</v>
+      </c>
+      <c r="C512" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="B512" s="1">
-        <v>3</v>
-      </c>
-      <c r="C512" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="D512" s="1" t="s">
         <v>7</v>
@@ -12706,13 +12703,13 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B513" s="1">
+        <v>3</v>
+      </c>
+      <c r="C513" s="1" t="s">
         <v>1039</v>
-      </c>
-      <c r="B513" s="1">
-        <v>3</v>
-      </c>
-      <c r="C513" s="1" t="s">
-        <v>1040</v>
       </c>
       <c r="D513" s="1" t="s">
         <v>7</v>
@@ -12723,13 +12720,13 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B514" s="1">
+        <v>3</v>
+      </c>
+      <c r="C514" s="1" t="s">
         <v>1041</v>
-      </c>
-      <c r="B514" s="1">
-        <v>3</v>
-      </c>
-      <c r="C514" s="1" t="s">
-        <v>1042</v>
       </c>
       <c r="D514" s="1" t="s">
         <v>7</v>
@@ -12740,13 +12737,13 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B515" s="1">
+        <v>3</v>
+      </c>
+      <c r="C515" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="B515" s="1">
-        <v>3</v>
-      </c>
-      <c r="C515" s="1" t="s">
-        <v>1044</v>
       </c>
       <c r="D515" s="1" t="s">
         <v>7</v>
@@ -12757,13 +12754,13 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B516" s="1">
+        <v>3</v>
+      </c>
+      <c r="C516" s="1" t="s">
         <v>1045</v>
-      </c>
-      <c r="B516" s="1">
-        <v>3</v>
-      </c>
-      <c r="C516" s="1" t="s">
-        <v>1046</v>
       </c>
       <c r="D516" s="1" t="s">
         <v>7</v>
@@ -12774,13 +12771,13 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B517" s="1">
+        <v>3</v>
+      </c>
+      <c r="C517" s="1" t="s">
         <v>1047</v>
-      </c>
-      <c r="B517" s="1">
-        <v>3</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>1048</v>
       </c>
       <c r="D517" s="1" t="s">
         <v>11</v>
@@ -12791,13 +12788,13 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B518" s="1">
+        <v>3</v>
+      </c>
+      <c r="C518" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="B518" s="1">
-        <v>3</v>
-      </c>
-      <c r="C518" s="1" t="s">
-        <v>1050</v>
       </c>
       <c r="D518" s="1" t="s">
         <v>11</v>
@@ -12808,13 +12805,13 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B519" s="1">
+        <v>3</v>
+      </c>
+      <c r="C519" s="1" t="s">
         <v>1051</v>
-      </c>
-      <c r="B519" s="1">
-        <v>3</v>
-      </c>
-      <c r="C519" s="1" t="s">
-        <v>1052</v>
       </c>
       <c r="D519" s="1" t="s">
         <v>11</v>
@@ -12825,13 +12822,13 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B520" s="1">
+        <v>3</v>
+      </c>
+      <c r="C520" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="B520" s="1">
-        <v>3</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>1054</v>
       </c>
       <c r="D520" s="1" t="s">
         <v>11</v>
@@ -12842,13 +12839,13 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B521" s="1">
+        <v>3</v>
+      </c>
+      <c r="C521" s="1" t="s">
         <v>1055</v>
-      </c>
-      <c r="B521" s="1">
-        <v>3</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>1056</v>
       </c>
       <c r="D521" s="1" t="s">
         <v>7</v>
@@ -12859,13 +12856,13 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B522" s="1">
+        <v>3</v>
+      </c>
+      <c r="C522" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="B522" s="1">
-        <v>3</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="D522" s="1" t="s">
         <v>11</v>
@@ -12876,13 +12873,13 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B523" s="1">
+        <v>3</v>
+      </c>
+      <c r="C523" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="B523" s="1">
-        <v>3</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>1060</v>
       </c>
       <c r="D523" s="1" t="s">
         <v>7</v>
@@ -12893,13 +12890,13 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B524" s="1">
+        <v>3</v>
+      </c>
+      <c r="C524" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="B524" s="1">
-        <v>3</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="D524" s="1" t="s">
         <v>11</v>
@@ -12910,13 +12907,13 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B525" s="1">
+        <v>3</v>
+      </c>
+      <c r="C525" s="1" t="s">
         <v>1063</v>
-      </c>
-      <c r="B525" s="1">
-        <v>3</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>1064</v>
       </c>
       <c r="D525" s="1" t="s">
         <v>7</v>
@@ -12927,13 +12924,13 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B526" s="1">
+        <v>3</v>
+      </c>
+      <c r="C526" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="B526" s="1">
-        <v>3</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="D526" s="1" t="s">
         <v>7</v>
@@ -12944,13 +12941,13 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B527" s="1">
+        <v>3</v>
+      </c>
+      <c r="C527" s="1" t="s">
         <v>1067</v>
-      </c>
-      <c r="B527" s="1">
-        <v>3</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>1068</v>
       </c>
       <c r="D527" s="1" t="s">
         <v>7</v>
@@ -12961,13 +12958,13 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B528" s="1">
+        <v>3</v>
+      </c>
+      <c r="C528" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="B528" s="1">
-        <v>3</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="D528" s="1" t="s">
         <v>7</v>
@@ -12978,13 +12975,13 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B529" s="1">
+        <v>3</v>
+      </c>
+      <c r="C529" s="1" t="s">
         <v>1071</v>
-      </c>
-      <c r="B529" s="1">
-        <v>3</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>1072</v>
       </c>
       <c r="D529" s="1" t="s">
         <v>7</v>
@@ -12995,13 +12992,13 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B530" s="1">
+        <v>3</v>
+      </c>
+      <c r="C530" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="B530" s="1">
-        <v>3</v>
-      </c>
-      <c r="C530" s="1" t="s">
-        <v>1074</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>7</v>
@@ -13012,13 +13009,13 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B531" s="1">
+        <v>3</v>
+      </c>
+      <c r="C531" s="1" t="s">
         <v>1075</v>
-      </c>
-      <c r="B531" s="1">
-        <v>3</v>
-      </c>
-      <c r="C531" s="1" t="s">
-        <v>1076</v>
       </c>
       <c r="D531" s="1" t="s">
         <v>7</v>
@@ -13029,13 +13026,13 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B532" s="1">
+        <v>3</v>
+      </c>
+      <c r="C532" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="B532" s="1">
-        <v>3</v>
-      </c>
-      <c r="C532" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="D532" s="1" t="s">
         <v>7</v>
@@ -13046,13 +13043,13 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B533" s="1">
+        <v>3</v>
+      </c>
+      <c r="C533" s="1" t="s">
         <v>1079</v>
-      </c>
-      <c r="B533" s="1">
-        <v>3</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>1080</v>
       </c>
       <c r="D533" s="1" t="s">
         <v>7</v>
@@ -13063,13 +13060,13 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B534" s="1">
+        <v>3</v>
+      </c>
+      <c r="C534" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="B534" s="1">
-        <v>3</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>1082</v>
       </c>
       <c r="D534" s="1" t="s">
         <v>7</v>
@@ -13080,13 +13077,13 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B535" s="1">
+        <v>3</v>
+      </c>
+      <c r="C535" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="B535" s="1">
-        <v>3</v>
-      </c>
-      <c r="C535" s="1" t="s">
-        <v>1084</v>
       </c>
       <c r="D535" s="1" t="s">
         <v>11</v>
@@ -13097,13 +13094,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B536" s="1">
+        <v>3</v>
+      </c>
+      <c r="C536" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="B536" s="1">
-        <v>3</v>
-      </c>
-      <c r="C536" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="D536" s="1" t="s">
         <v>7</v>
@@ -13114,13 +13111,13 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B537" s="1">
+        <v>3</v>
+      </c>
+      <c r="C537" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="B537" s="1">
-        <v>3</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>1088</v>
       </c>
       <c r="D537" s="1" t="s">
         <v>7</v>
@@ -13131,13 +13128,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B538" s="1">
+        <v>3</v>
+      </c>
+      <c r="C538" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="B538" s="1">
-        <v>3</v>
-      </c>
-      <c r="C538" s="1" t="s">
-        <v>1090</v>
       </c>
       <c r="D538" s="1" t="s">
         <v>7</v>
@@ -13148,13 +13145,13 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B539" s="1">
+        <v>3</v>
+      </c>
+      <c r="C539" s="1" t="s">
         <v>1091</v>
-      </c>
-      <c r="B539" s="1">
-        <v>3</v>
-      </c>
-      <c r="C539" s="1" t="s">
-        <v>1092</v>
       </c>
       <c r="D539" s="1" t="s">
         <v>11</v>
@@ -13165,13 +13162,13 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B540" s="1">
+        <v>3</v>
+      </c>
+      <c r="C540" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="B540" s="1">
-        <v>3</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="D540" s="1" t="s">
         <v>7</v>
@@ -13182,13 +13179,13 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B541" s="1">
+        <v>3</v>
+      </c>
+      <c r="C541" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="B541" s="1">
-        <v>3</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>1096</v>
       </c>
       <c r="D541" s="1" t="s">
         <v>7</v>
@@ -13199,13 +13196,13 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B542" s="1">
+        <v>3</v>
+      </c>
+      <c r="C542" s="1" t="s">
         <v>1097</v>
-      </c>
-      <c r="B542" s="1">
-        <v>3</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>1098</v>
       </c>
       <c r="D542" s="1" t="s">
         <v>7</v>
@@ -13216,13 +13213,13 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B543" s="1">
+        <v>3</v>
+      </c>
+      <c r="C543" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="B543" s="1">
-        <v>3</v>
-      </c>
-      <c r="C543" s="1" t="s">
-        <v>1100</v>
       </c>
       <c r="D543" s="1" t="s">
         <v>11</v>
@@ -13233,13 +13230,13 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B544" s="1">
+        <v>3</v>
+      </c>
+      <c r="C544" s="1" t="s">
         <v>1101</v>
-      </c>
-      <c r="B544" s="1">
-        <v>3</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>1102</v>
       </c>
       <c r="D544" s="1" t="s">
         <v>7</v>
@@ -13250,13 +13247,13 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B545" s="1">
+        <v>3</v>
+      </c>
+      <c r="C545" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="B545" s="1">
-        <v>3</v>
-      </c>
-      <c r="C545" s="1" t="s">
-        <v>1104</v>
       </c>
       <c r="D545" s="1" t="s">
         <v>7</v>
@@ -13267,13 +13264,13 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B546" s="1">
+        <v>3</v>
+      </c>
+      <c r="C546" s="1" t="s">
         <v>1105</v>
-      </c>
-      <c r="B546" s="1">
-        <v>3</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>1106</v>
       </c>
       <c r="D546" s="1" t="s">
         <v>11</v>
@@ -13284,13 +13281,13 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B547" s="1">
+        <v>3</v>
+      </c>
+      <c r="C547" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="B547" s="1">
-        <v>3</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="D547" s="1" t="s">
         <v>11</v>
@@ -13301,13 +13298,13 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B548" s="1">
+        <v>3</v>
+      </c>
+      <c r="C548" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="B548" s="1">
-        <v>3</v>
-      </c>
-      <c r="C548" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="D548" s="1" t="s">
         <v>11</v>
@@ -13318,13 +13315,13 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B549" s="1">
+        <v>3</v>
+      </c>
+      <c r="C549" s="1" t="s">
         <v>1111</v>
-      </c>
-      <c r="B549" s="1">
-        <v>3</v>
-      </c>
-      <c r="C549" s="1" t="s">
-        <v>1112</v>
       </c>
       <c r="D549" s="1" t="s">
         <v>11</v>
@@ -13335,13 +13332,13 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B550" s="1">
+        <v>3</v>
+      </c>
+      <c r="C550" s="1" t="s">
         <v>1113</v>
-      </c>
-      <c r="B550" s="1">
-        <v>3</v>
-      </c>
-      <c r="C550" s="1" t="s">
-        <v>1114</v>
       </c>
       <c r="D550" s="1" t="s">
         <v>11</v>
@@ -13352,13 +13349,13 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B551" s="1">
+        <v>3</v>
+      </c>
+      <c r="C551" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="B551" s="1">
-        <v>3</v>
-      </c>
-      <c r="C551" s="1" t="s">
-        <v>1116</v>
       </c>
       <c r="D551" s="1" t="s">
         <v>11</v>
@@ -13369,13 +13366,13 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B552" s="1">
+        <v>3</v>
+      </c>
+      <c r="C552" s="1" t="s">
         <v>1117</v>
-      </c>
-      <c r="B552" s="1">
-        <v>3</v>
-      </c>
-      <c r="C552" s="1" t="s">
-        <v>1118</v>
       </c>
       <c r="D552" s="1" t="s">
         <v>7</v>
@@ -13386,13 +13383,13 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B553" s="1">
+        <v>3</v>
+      </c>
+      <c r="C553" s="1" t="s">
         <v>1119</v>
-      </c>
-      <c r="B553" s="1">
-        <v>3</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>1120</v>
       </c>
       <c r="D553" s="1" t="s">
         <v>11</v>
@@ -13403,13 +13400,13 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B554" s="1">
+        <v>3</v>
+      </c>
+      <c r="C554" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="B554" s="1">
-        <v>3</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>1122</v>
       </c>
       <c r="D554" s="1" t="s">
         <v>7</v>
@@ -13420,13 +13417,13 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B555" s="1">
+        <v>3</v>
+      </c>
+      <c r="C555" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="B555" s="1">
-        <v>3</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>1124</v>
       </c>
       <c r="D555" s="1" t="s">
         <v>11</v>
@@ -13437,13 +13434,13 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B556" s="1">
+        <v>3</v>
+      </c>
+      <c r="C556" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="B556" s="1">
-        <v>3</v>
-      </c>
-      <c r="C556" s="1" t="s">
-        <v>1126</v>
       </c>
       <c r="D556" s="1" t="s">
         <v>7</v>
@@ -13454,13 +13451,13 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B557" s="1">
+        <v>3</v>
+      </c>
+      <c r="C557" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="B557" s="1">
-        <v>3</v>
-      </c>
-      <c r="C557" s="1" t="s">
-        <v>1128</v>
       </c>
       <c r="D557" s="1" t="s">
         <v>11</v>
@@ -13471,13 +13468,13 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B558" s="1">
+        <v>3</v>
+      </c>
+      <c r="C558" s="1" t="s">
         <v>1129</v>
-      </c>
-      <c r="B558" s="1">
-        <v>3</v>
-      </c>
-      <c r="C558" s="1" t="s">
-        <v>1130</v>
       </c>
       <c r="D558" s="1" t="s">
         <v>11</v>
@@ -13488,13 +13485,13 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B559" s="1">
+        <v>3</v>
+      </c>
+      <c r="C559" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="B559" s="1">
-        <v>3</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>1132</v>
       </c>
       <c r="D559" s="1" t="s">
         <v>11</v>
@@ -13505,13 +13502,13 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B560" s="1">
+        <v>3</v>
+      </c>
+      <c r="C560" s="1" t="s">
         <v>1133</v>
-      </c>
-      <c r="B560" s="1">
-        <v>3</v>
-      </c>
-      <c r="C560" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="D560" s="1" t="s">
         <v>7</v>
@@ -13522,13 +13519,13 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B561" s="1">
+        <v>3</v>
+      </c>
+      <c r="C561" s="1" t="s">
         <v>1135</v>
-      </c>
-      <c r="B561" s="1">
-        <v>3</v>
-      </c>
-      <c r="C561" s="1" t="s">
-        <v>1136</v>
       </c>
       <c r="D561" s="1" t="s">
         <v>7</v>
@@ -13539,13 +13536,13 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B562" s="1">
+        <v>3</v>
+      </c>
+      <c r="C562" s="1" t="s">
         <v>1137</v>
-      </c>
-      <c r="B562" s="1">
-        <v>3</v>
-      </c>
-      <c r="C562" s="1" t="s">
-        <v>1138</v>
       </c>
       <c r="D562" s="1" t="s">
         <v>11</v>
@@ -13556,13 +13553,13 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B563" s="1">
+        <v>3</v>
+      </c>
+      <c r="C563" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="B563" s="1">
-        <v>3</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>1140</v>
       </c>
       <c r="D563" s="1" t="s">
         <v>11</v>
@@ -13573,13 +13570,13 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B564" s="1">
+        <v>3</v>
+      </c>
+      <c r="C564" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="B564" s="1">
-        <v>3</v>
-      </c>
-      <c r="C564" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="D564" s="1" t="s">
         <v>11</v>
@@ -13590,13 +13587,13 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B565" s="1">
+        <v>3</v>
+      </c>
+      <c r="C565" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="B565" s="1">
-        <v>3</v>
-      </c>
-      <c r="C565" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="D565" s="1" t="s">
         <v>7</v>
@@ -13607,13 +13604,13 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B566" s="1">
+        <v>3</v>
+      </c>
+      <c r="C566" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="B566" s="1">
-        <v>3</v>
-      </c>
-      <c r="C566" s="1" t="s">
-        <v>1146</v>
       </c>
       <c r="D566" s="1" t="s">
         <v>7</v>
@@ -13624,13 +13621,13 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B567" s="1">
+        <v>3</v>
+      </c>
+      <c r="C567" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="B567" s="1">
-        <v>3</v>
-      </c>
-      <c r="C567" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="D567" s="1" t="s">
         <v>11</v>
@@ -13641,13 +13638,13 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B568" s="1">
+        <v>3</v>
+      </c>
+      <c r="C568" s="1" t="s">
         <v>1149</v>
-      </c>
-      <c r="B568" s="1">
-        <v>3</v>
-      </c>
-      <c r="C568" s="1" t="s">
-        <v>1150</v>
       </c>
       <c r="D568" s="1" t="s">
         <v>7</v>
@@ -13658,13 +13655,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B569" s="1">
+        <v>3</v>
+      </c>
+      <c r="C569" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="B569" s="1">
-        <v>3</v>
-      </c>
-      <c r="C569" s="1" t="s">
-        <v>1152</v>
       </c>
       <c r="D569" s="1" t="s">
         <v>11</v>
